--- a/data/seeds/questionnaire_data_default.xlsx
+++ b/data/seeds/questionnaire_data_default.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="answers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="answers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1097,15 +1097,19 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>COST-001</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>kpi</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>経営方針・中期計画</t>
+          <t>cost_document</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1197,15 +1201,19 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>COST-002</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>kpi</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>経営方針・中期計画</t>
+          <t>cost_document</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1297,15 +1305,19 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>COST-003</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>kpi</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>経営方針・中期計画</t>
+          <t>cost_document</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1397,15 +1409,19 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>COST-004</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>kpi</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>経営方針・中期計画</t>
+          <t>cost_document</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1497,15 +1513,19 @@
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>COST-005</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>kpi</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>経営方針・中期計画</t>
+          <t>cost_document</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
